--- a/Chapter-6b/4 - OT - Checklist for Procedures and Furniture Requirements.xlsx
+++ b/Chapter-6b/4 - OT - Checklist for Procedures and Furniture Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\Architecture Manual\3 - Final Version - Under Review\Section 6b - Operation theatre &amp; sterilisation process\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasipriyakarumanchi/Library/CloudStorage/GoogleDrive-sashi@aravind.org/My Drive/Architecture Manual/3 - Final Version - Under Review/Section 6b - Operation theatre &amp; sterilisation process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2B99E4-DAE3-4CC5-83E1-BC3AF7AC2D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8567F07D-B4D0-D64A-99B0-5088E657E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E0069D1-7A52-4049-A928-7B9398C1BAB7}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20060" xr2:uid="{4E0069D1-7A52-4049-A928-7B9398C1BAB7}"/>
   </bookViews>
   <sheets>
     <sheet name="OT - Procedures &amp; Furniture" sheetId="1" r:id="rId1"/>
@@ -38,10 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="73">
-  <si>
-    <t>Version : Phase -1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="71">
   <si>
     <t>Room Name</t>
   </si>
@@ -110,9 +107,6 @@
   </si>
   <si>
     <t>S No</t>
-  </si>
-  <si>
-    <t>Doc. No. 1240-A-Doc-042 V1 R0/OCT-14</t>
   </si>
   <si>
     <t>ü</t>
@@ -146,21 +140,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Section 5b - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Century Gothic"/>
-        <family val="2"/>
-      </rPr>
-      <t>Guidelines for OT and Ward</t>
-    </r>
-  </si>
-  <si>
     <t>Restricted corridor</t>
   </si>
   <si>
@@ -291,6 +270,9 @@
   </si>
   <si>
     <t xml:space="preserve">Tables/racks/stools - SS material preferred </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard Architectural Modules for Layouts </t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1118,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1392,6 +1374,43 @@
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="17" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1418,42 +1437,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="17" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1474,9 +1459,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1514,7 +1499,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1620,7 +1605,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1762,7 +1747,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1774,92 +1759,90 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T46"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15.5" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="59.76953125" style="1" customWidth="1"/>
-    <col min="3" max="5" width="3.6796875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="6.453125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="3.6796875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="5.26953125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="59.83203125" style="1" customWidth="1"/>
+    <col min="3" max="5" width="3.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.5" style="2" customWidth="1"/>
+    <col min="7" max="8" width="3.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" style="2" customWidth="1"/>
     <col min="10" max="11" width="4" style="2" customWidth="1"/>
-    <col min="12" max="12" width="4.6328125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="6.6796875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="5.36328125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="4.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="5.33203125" style="2" customWidth="1"/>
     <col min="15" max="16" width="4" style="2" customWidth="1"/>
-    <col min="17" max="17" width="5.31640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="4.26953125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="38.26953125" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.81640625" style="1"/>
+    <col min="17" max="17" width="5.33203125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="4.33203125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="38.33203125" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="3" customFormat="1" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-    </row>
-    <row r="2" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A2" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="94"/>
-      <c r="Q2" s="94"/>
-      <c r="R2" s="94"/>
-    </row>
-    <row r="3" spans="1:20" s="76" customFormat="1" ht="13.25" x14ac:dyDescent="0.6">
-      <c r="A3" s="92" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="92"/>
-      <c r="L3" s="92"/>
-      <c r="M3" s="92"/>
-      <c r="N3" s="92"/>
-      <c r="O3" s="92"/>
-      <c r="P3" s="92"/>
-      <c r="Q3" s="92"/>
-      <c r="R3" s="92"/>
-    </row>
-    <row r="4" spans="1:20" s="76" customFormat="1" ht="14" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:20" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="102" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
+      <c r="R1" s="86"/>
+    </row>
+    <row r="2" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="86"/>
+      <c r="R2" s="86"/>
+    </row>
+    <row r="3" spans="1:20" s="76" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+      <c r="A3" s="84"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="84"/>
+    </row>
+    <row r="4" spans="1:20" s="76" customFormat="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="77"/>
       <c r="B4" s="75"/>
       <c r="C4" s="78"/>
@@ -1877,123 +1860,121 @@
       <c r="O4" s="78"/>
       <c r="P4" s="78"/>
       <c r="Q4" s="78"/>
-      <c r="R4" s="80" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" s="4" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A5" s="95" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="97" t="s">
+      <c r="R4" s="80"/>
+    </row>
+    <row r="5" spans="1:20" s="4" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="87" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="99" t="s">
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="99" t="s">
+      <c r="L5" s="92"/>
+      <c r="M5" s="92"/>
+      <c r="N5" s="92"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="92"/>
+      <c r="Q5" s="92"/>
+      <c r="R5" s="93"/>
+      <c r="S5" s="94" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="74" customFormat="1" ht="85.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="88"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="69" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="100"/>
-      <c r="M5" s="100"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="100"/>
-      <c r="R5" s="101"/>
-      <c r="S5" s="84" t="s">
+      <c r="F6" s="81" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" s="74" customFormat="1" ht="85.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A6" s="96"/>
-      <c r="B6" s="98"/>
-      <c r="C6" s="69" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="69" t="s">
+      <c r="G6" s="70" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="81" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="70" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="82" t="s">
-        <v>5</v>
-      </c>
       <c r="I6" s="83" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J6" s="72"/>
       <c r="K6" s="71" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="71" t="s">
+      <c r="M6" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="O6" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="N6" s="71" t="s">
-        <v>48</v>
-      </c>
-      <c r="O6" s="70" t="s">
+      <c r="P6" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q6" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="P6" s="70" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q6" s="83" t="s">
+      <c r="R6" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="S6" s="95"/>
+    </row>
+    <row r="7" spans="1:20" s="38" customFormat="1" ht="19.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="R6" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="S6" s="85"/>
-    </row>
-    <row r="7" spans="1:20" s="38" customFormat="1" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A7" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="86" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="87"/>
-      <c r="L7" s="87"/>
-      <c r="M7" s="87"/>
-      <c r="N7" s="87"/>
-      <c r="O7" s="87"/>
-      <c r="P7" s="87"/>
-      <c r="Q7" s="87"/>
-      <c r="R7" s="88"/>
+      <c r="B7" s="96" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="97"/>
+      <c r="P7" s="97"/>
+      <c r="Q7" s="97"/>
+      <c r="R7" s="98"/>
       <c r="S7" s="55"/>
     </row>
-    <row r="8" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="41" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
@@ -2013,55 +1994,55 @@
       <c r="R8" s="32"/>
       <c r="S8" s="53"/>
     </row>
-    <row r="9" spans="1:20" s="3" customFormat="1" ht="29.7" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:20" s="3" customFormat="1" ht="29.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="41">
         <v>1</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S9" s="49" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="T9" s="5"/>
     </row>
-    <row r="10" spans="1:20" s="3" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:20" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="41">
         <v>2</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -2071,10 +2052,10 @@
       <c r="I10" s="8"/>
       <c r="J10" s="10"/>
       <c r="K10" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L10" s="47" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
@@ -2082,69 +2063,69 @@
       <c r="P10" s="13"/>
       <c r="Q10" s="8"/>
       <c r="R10" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S10" s="49"/>
       <c r="T10" s="5"/>
     </row>
-    <row r="11" spans="1:20" s="3" customFormat="1" ht="46.5" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:20" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="41">
         <v>3</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O11" s="13"/>
       <c r="P11" s="13"/>
       <c r="Q11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R11" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S11" s="49" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="T11" s="5"/>
     </row>
-    <row r="12" spans="1:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:20" s="3" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="41">
         <v>4</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="16"/>
@@ -2165,65 +2146,65 @@
       <c r="S12" s="49"/>
       <c r="T12" s="5"/>
     </row>
-    <row r="13" spans="1:20" s="3" customFormat="1" ht="29.7" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:20" s="3" customFormat="1" ht="29.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="41">
         <v>4.0999999999999996</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O13" s="15"/>
       <c r="P13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R13" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S13" s="56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" s="3" customFormat="1" ht="29.15" customHeight="1" x14ac:dyDescent="0.75">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" s="3" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="41">
         <v>4.2</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
@@ -2239,122 +2220,122 @@
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
       <c r="P14" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q14" s="15"/>
       <c r="R14" s="19"/>
       <c r="S14" s="50"/>
     </row>
-    <row r="15" spans="1:20" s="3" customFormat="1" ht="28.75" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:20" s="3" customFormat="1" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="41">
         <v>5</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O15" s="15"/>
       <c r="P15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R15" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S15" s="50"/>
     </row>
-    <row r="16" spans="1:20" s="3" customFormat="1" ht="28.9" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:20" s="3" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="41">
         <v>6</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J16" s="10"/>
       <c r="K16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P16" s="8"/>
       <c r="Q16" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R16" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S16" s="56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.75">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" s="3" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="41" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B17" s="48" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="16"/>
@@ -2375,12 +2356,12 @@
       <c r="S17" s="49"/>
       <c r="T17" s="5"/>
     </row>
-    <row r="18" spans="1:20" s="3" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:20" s="3" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="41">
         <v>7</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -2400,19 +2381,19 @@
       <c r="R18" s="14"/>
       <c r="S18" s="50"/>
     </row>
-    <row r="19" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="41">
         <v>7.1</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
@@ -2427,23 +2408,23 @@
       <c r="P19" s="15"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S19" s="50"/>
     </row>
-    <row r="20" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="41">
         <v>7.2</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
@@ -2452,7 +2433,7 @@
       <c r="J20" s="10"/>
       <c r="K20" s="11"/>
       <c r="L20" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
@@ -2460,23 +2441,23 @@
       <c r="P20" s="13"/>
       <c r="Q20" s="15"/>
       <c r="R20" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S20" s="50"/>
     </row>
-    <row r="21" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="41">
         <v>7.3</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
@@ -2491,23 +2472,23 @@
       <c r="P21" s="15"/>
       <c r="Q21" s="15"/>
       <c r="R21" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S21" s="50"/>
     </row>
-    <row r="22" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="41">
         <v>7.4</v>
       </c>
       <c r="B22" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
@@ -2522,16 +2503,16 @@
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S22" s="50"/>
     </row>
-    <row r="23" spans="1:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:20" s="3" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="41">
         <v>8</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="16"/>
@@ -2552,19 +2533,19 @@
       <c r="S23" s="49"/>
       <c r="T23" s="5"/>
     </row>
-    <row r="24" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="41">
         <v>8.1</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
@@ -2579,25 +2560,25 @@
       <c r="P24" s="16"/>
       <c r="Q24" s="20"/>
       <c r="R24" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="S24" s="89" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+        <v>23</v>
+      </c>
+      <c r="S24" s="99" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="41">
         <v>8.1999999999999993</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F25" s="20"/>
       <c r="G25" s="20"/>
@@ -2612,23 +2593,23 @@
       <c r="P25" s="16"/>
       <c r="Q25" s="20"/>
       <c r="R25" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="S25" s="90"/>
-    </row>
-    <row r="26" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+        <v>23</v>
+      </c>
+      <c r="S25" s="100"/>
+    </row>
+    <row r="26" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="41">
         <v>8.3000000000000007</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
@@ -2643,16 +2624,16 @@
       <c r="P26" s="16"/>
       <c r="Q26" s="20"/>
       <c r="R26" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="S26" s="91"/>
-    </row>
-    <row r="27" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+        <v>23</v>
+      </c>
+      <c r="S26" s="101"/>
+    </row>
+    <row r="27" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="41">
         <v>9</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -2670,41 +2651,41 @@
       <c r="P27" s="34"/>
       <c r="Q27" s="20"/>
       <c r="R27" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S27" s="52"/>
     </row>
-    <row r="28" spans="1:20" s="38" customFormat="1" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="28" spans="1:20" s="38" customFormat="1" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="86" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="87"/>
-      <c r="D28" s="87"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="87"/>
-      <c r="G28" s="87"/>
-      <c r="H28" s="87"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="K28" s="87"/>
-      <c r="L28" s="87"/>
-      <c r="M28" s="87"/>
-      <c r="N28" s="87"/>
-      <c r="O28" s="87"/>
-      <c r="P28" s="87"/>
-      <c r="Q28" s="87"/>
-      <c r="R28" s="88"/>
+        <v>17</v>
+      </c>
+      <c r="B28" s="96" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="97"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="97"/>
+      <c r="L28" s="97"/>
+      <c r="M28" s="97"/>
+      <c r="N28" s="97"/>
+      <c r="O28" s="97"/>
+      <c r="P28" s="97"/>
+      <c r="Q28" s="97"/>
+      <c r="R28" s="98"/>
       <c r="S28" s="54"/>
     </row>
-    <row r="29" spans="1:20" s="3" customFormat="1" ht="33.65" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:20" s="3" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="41">
         <v>6</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -2713,11 +2694,11 @@
       <c r="G29" s="16"/>
       <c r="H29" s="16"/>
       <c r="I29" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J29" s="10"/>
       <c r="K29" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L29" s="29"/>
       <c r="M29" s="9"/>
@@ -2727,18 +2708,18 @@
       <c r="Q29" s="31"/>
       <c r="R29" s="32"/>
       <c r="S29" s="68" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="41">
         <v>7</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D30" s="57"/>
       <c r="E30" s="16"/>
@@ -2757,12 +2738,12 @@
       <c r="R30" s="33"/>
       <c r="S30" s="50"/>
     </row>
-    <row r="31" spans="1:20" s="3" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:20" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="41">
         <v>8</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C31" s="34"/>
       <c r="D31" s="34"/>
@@ -2779,17 +2760,17 @@
       <c r="O31" s="16"/>
       <c r="P31" s="16"/>
       <c r="Q31" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R31" s="33"/>
       <c r="S31" s="50"/>
     </row>
-    <row r="32" spans="1:20" s="3" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:20" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="41">
         <v>9</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C32" s="34"/>
       <c r="D32" s="34"/>
@@ -2800,7 +2781,7 @@
       <c r="I32" s="17"/>
       <c r="J32" s="10"/>
       <c r="K32" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L32" s="17"/>
       <c r="M32" s="20"/>
@@ -2811,98 +2792,98 @@
       <c r="R32" s="33"/>
       <c r="S32" s="50"/>
     </row>
-    <row r="33" spans="1:19" s="3" customFormat="1" ht="30.9" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:19" s="3" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="41">
         <v>10</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C33" s="34"/>
       <c r="D33" s="34"/>
       <c r="E33" s="34"/>
       <c r="F33" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J33" s="10"/>
       <c r="K33" s="18"/>
       <c r="L33" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N33" s="15"/>
       <c r="O33" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P33" s="16"/>
       <c r="Q33" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R33" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S33" s="56" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="41">
         <v>11</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C34" s="34"/>
       <c r="D34" s="34"/>
       <c r="E34" s="34"/>
       <c r="F34" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H34" s="8"/>
       <c r="I34" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J34" s="10"/>
       <c r="K34" s="18"/>
       <c r="L34" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N34" s="15"/>
       <c r="O34" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P34" s="16"/>
       <c r="Q34" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R34" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S34" s="50"/>
     </row>
-    <row r="35" spans="1:19" s="3" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:19" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="41">
         <v>12</v>
       </c>
       <c r="B35" s="40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
@@ -2910,10 +2891,10 @@
       <c r="F35" s="16"/>
       <c r="G35" s="16"/>
       <c r="H35" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="21"/>
@@ -2924,20 +2905,20 @@
       <c r="P35" s="16"/>
       <c r="Q35" s="20"/>
       <c r="R35" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S35" s="50"/>
     </row>
-    <row r="36" spans="1:19" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:19" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A36" s="41">
         <v>13</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C36" s="16"/>
       <c r="D36" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E36" s="16"/>
       <c r="F36" s="16"/>
@@ -2954,15 +2935,15 @@
       <c r="Q36" s="20"/>
       <c r="R36" s="14"/>
       <c r="S36" s="59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" s="3" customFormat="1" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="41">
         <v>14</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
@@ -2980,39 +2961,39 @@
       <c r="P37" s="34"/>
       <c r="Q37" s="20"/>
       <c r="R37" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S37" s="52"/>
     </row>
-    <row r="38" spans="1:19" s="38" customFormat="1" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="38" spans="1:19" s="38" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" s="87"/>
-      <c r="D38" s="87"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="87"/>
-      <c r="G38" s="87"/>
-      <c r="H38" s="87"/>
-      <c r="I38" s="87"/>
-      <c r="J38" s="87"/>
-      <c r="K38" s="87"/>
-      <c r="L38" s="87"/>
-      <c r="M38" s="87"/>
-      <c r="N38" s="87"/>
-      <c r="O38" s="87"/>
-      <c r="P38" s="87"/>
-      <c r="Q38" s="87"/>
-      <c r="R38" s="88"/>
+        <v>10</v>
+      </c>
+      <c r="B38" s="96" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="97"/>
+      <c r="D38" s="97"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="97"/>
+      <c r="G38" s="97"/>
+      <c r="H38" s="97"/>
+      <c r="I38" s="97"/>
+      <c r="J38" s="97"/>
+      <c r="K38" s="97"/>
+      <c r="L38" s="97"/>
+      <c r="M38" s="97"/>
+      <c r="N38" s="97"/>
+      <c r="O38" s="97"/>
+      <c r="P38" s="97"/>
+      <c r="Q38" s="97"/>
+      <c r="R38" s="98"/>
       <c r="S38" s="55"/>
     </row>
-    <row r="39" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="60"/>
       <c r="B39" s="62" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C39" s="16"/>
       <c r="D39" s="16"/>
@@ -3032,7 +3013,7 @@
       <c r="R39" s="19"/>
       <c r="S39" s="53"/>
     </row>
-    <row r="40" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="61"/>
       <c r="B40" s="63"/>
       <c r="C40" s="16"/>
@@ -3053,7 +3034,7 @@
       <c r="R40" s="19"/>
       <c r="S40" s="50"/>
     </row>
-    <row r="41" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="41" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="64"/>
       <c r="C41" s="16"/>
@@ -3074,37 +3055,37 @@
       <c r="R41" s="19"/>
       <c r="S41" s="50"/>
     </row>
-    <row r="42" spans="1:19" s="38" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="42" spans="1:19" s="38" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="B42" s="86" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="87"/>
-      <c r="D42" s="87"/>
-      <c r="E42" s="87"/>
-      <c r="F42" s="87"/>
-      <c r="G42" s="87"/>
-      <c r="H42" s="87"/>
-      <c r="I42" s="87"/>
-      <c r="J42" s="87"/>
-      <c r="K42" s="87"/>
-      <c r="L42" s="87"/>
-      <c r="M42" s="87"/>
-      <c r="N42" s="87"/>
-      <c r="O42" s="87"/>
-      <c r="P42" s="87"/>
-      <c r="Q42" s="87"/>
-      <c r="R42" s="88"/>
+        <v>58</v>
+      </c>
+      <c r="B42" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="97"/>
+      <c r="D42" s="97"/>
+      <c r="E42" s="97"/>
+      <c r="F42" s="97"/>
+      <c r="G42" s="97"/>
+      <c r="H42" s="97"/>
+      <c r="I42" s="97"/>
+      <c r="J42" s="97"/>
+      <c r="K42" s="97"/>
+      <c r="L42" s="97"/>
+      <c r="M42" s="97"/>
+      <c r="N42" s="97"/>
+      <c r="O42" s="97"/>
+      <c r="P42" s="97"/>
+      <c r="Q42" s="97"/>
+      <c r="R42" s="98"/>
       <c r="S42" s="55"/>
     </row>
-    <row r="43" spans="1:19" s="3" customFormat="1" ht="29.15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:19" s="3" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="60">
         <v>15</v>
       </c>
       <c r="B43" s="65" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
@@ -3124,7 +3105,7 @@
       <c r="R43" s="19"/>
       <c r="S43" s="50"/>
     </row>
-    <row r="44" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="44" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="67"/>
       <c r="B44" s="66"/>
       <c r="C44" s="44"/>
@@ -3145,13 +3126,19 @@
       <c r="R44" s="36"/>
       <c r="S44" s="51"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="B42:R42"/>
+    <mergeCell ref="B7:R7"/>
+    <mergeCell ref="B28:R28"/>
+    <mergeCell ref="B38:R38"/>
+    <mergeCell ref="S24:S26"/>
     <mergeCell ref="A3:R3"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A5:A6"/>
@@ -3159,12 +3146,6 @@
     <mergeCell ref="C5:I5"/>
     <mergeCell ref="K5:R5"/>
     <mergeCell ref="A2:R2"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="B42:R42"/>
-    <mergeCell ref="B7:R7"/>
-    <mergeCell ref="B28:R28"/>
-    <mergeCell ref="B38:R38"/>
-    <mergeCell ref="S24:S26"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
